--- a/Financial Analysis/WMT.xlsx
+++ b/Financial Analysis/WMT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Desktop\Financial Analysis\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AB29B07-0021-4A00-BC7F-B6DEB069A508}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E22C38-6EF7-4E64-921F-8987788E33B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4FE1C73D-B38E-414F-97D3-844DCE1F8905}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4FE1C73D-B38E-414F-97D3-844DCE1F8905}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -248,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -267,6 +267,7 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -288,14 +289,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>7620</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>22860</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>129540</xdr:rowOff>
     </xdr:to>
@@ -312,7 +313,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10629900" y="7620"/>
+          <a:off x="12070080" y="7620"/>
           <a:ext cx="0" cy="5974080"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -712,17 +713,17 @@
         <v>1</v>
       </c>
       <c r="D3" s="6">
-        <v>95.91</v>
+        <v>99.35</v>
       </c>
       <c r="E3" s="4">
-        <v>45772</v>
+        <v>45904</v>
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45773</v>
+        <v>45904</v>
       </c>
       <c r="G3" s="4">
-        <v>45792</v>
+        <v>45981</v>
       </c>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.3">
@@ -730,11 +731,11 @@
         <v>2</v>
       </c>
       <c r="D4" s="2">
-        <f>8016.8</f>
-        <v>8016.8</v>
+        <f>7972.9</f>
+        <v>7972.9</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.3">
@@ -743,7 +744,7 @@
       </c>
       <c r="D5" s="2">
         <f>D3*D4</f>
-        <v>768891.28799999994</v>
+        <v>792107.61499999987</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.3">
@@ -751,11 +752,11 @@
         <v>4</v>
       </c>
       <c r="D6" s="2">
-        <f>9037</f>
-        <v>9037</v>
+        <f>9431</f>
+        <v>9431</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.3">
@@ -763,11 +764,11 @@
         <v>5</v>
       </c>
       <c r="D7" s="2">
-        <f>3068+2598+33401</f>
-        <v>39067</v>
+        <f>3837+4011+35640</f>
+        <v>43488</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>34</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.3">
@@ -776,7 +777,7 @@
       </c>
       <c r="D8" s="2">
         <f>D6-D7</f>
-        <v>-30030</v>
+        <v>-34057</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.3">
@@ -785,7 +786,7 @@
       </c>
       <c r="D9" s="2">
         <f>D5-D8</f>
-        <v>798921.28799999994</v>
+        <v>826164.61499999987</v>
       </c>
     </row>
   </sheetData>
@@ -1053,10 +1054,20 @@
       <c r="N3" s="7">
         <v>180554</v>
       </c>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-      <c r="Q3" s="7"/>
-      <c r="R3" s="7"/>
+      <c r="O3" s="7">
+        <v>165609</v>
+      </c>
+      <c r="P3" s="7">
+        <v>177402</v>
+      </c>
+      <c r="Q3" s="7">
+        <f>M3*1.05</f>
+        <v>178067.4</v>
+      </c>
+      <c r="R3" s="7">
+        <f>N3*1.03</f>
+        <v>185970.62</v>
+      </c>
       <c r="T3" s="7">
         <v>523964</v>
       </c>
@@ -1079,48 +1090,48 @@
         <v>680985</v>
       </c>
       <c r="Z3" s="7">
-        <f>Y3*1.04</f>
-        <v>708224.4</v>
+        <f>SUM(O3:R3)</f>
+        <v>707049.02</v>
       </c>
       <c r="AA3" s="7">
         <f>Z3*1.03</f>
-        <v>729471.1320000001</v>
+        <v>728260.49060000002</v>
       </c>
       <c r="AB3" s="7">
         <f>AA3*1.02</f>
-        <v>744060.5546400001</v>
+        <v>742825.70041200006</v>
       </c>
       <c r="AC3" s="7">
         <f>AB3*1.02</f>
-        <v>758941.76573280012</v>
+        <v>757682.21442024002</v>
       </c>
       <c r="AD3" s="7">
         <f t="shared" ref="AD3:AE3" si="0">AC3*1.02</f>
-        <v>774120.60104745615</v>
+        <v>772835.85870864487</v>
       </c>
       <c r="AE3" s="7">
         <f t="shared" si="0"/>
-        <v>789603.01306840533</v>
+        <v>788292.57588281773</v>
       </c>
       <c r="AF3" s="7">
         <f>AE3*1.01</f>
-        <v>797499.04319908936</v>
+        <v>796175.50164164591</v>
       </c>
       <c r="AG3" s="7">
         <f t="shared" ref="AG3:AJ3" si="1">AF3*1.01</f>
-        <v>805474.0336310803</v>
+        <v>804137.25665806234</v>
       </c>
       <c r="AH3" s="7">
         <f t="shared" si="1"/>
-        <v>813528.77396739111</v>
+        <v>812178.62922464299</v>
       </c>
       <c r="AI3" s="7">
         <f t="shared" si="1"/>
-        <v>821664.06170706498</v>
+        <v>820300.41551688942</v>
       </c>
       <c r="AJ3" s="7">
         <f t="shared" si="1"/>
-        <v>829880.70232413558</v>
+        <v>828503.41967205831</v>
       </c>
     </row>
     <row r="4" spans="1:156" x14ac:dyDescent="0.3">
@@ -1163,10 +1174,20 @@
       <c r="N4" s="2">
         <v>136172</v>
       </c>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
+      <c r="O4" s="2">
+        <v>124303</v>
+      </c>
+      <c r="P4" s="2">
+        <v>132771</v>
+      </c>
+      <c r="Q4" s="2">
+        <f>Q3-Q5</f>
+        <v>133550.54999999999</v>
+      </c>
+      <c r="R4" s="2">
+        <f>R3-R5</f>
+        <v>139477.965</v>
+      </c>
       <c r="T4" s="2">
         <v>394605</v>
       </c>
@@ -1188,49 +1209,49 @@
         <f>SUM(K4:N4)</f>
         <v>511753</v>
       </c>
-      <c r="Z4" s="2">
-        <f>Z3-Z5</f>
-        <v>531168.30000000005</v>
+      <c r="Z4" s="12">
+        <f>SUM(O4:R4)</f>
+        <v>530102.51500000001</v>
       </c>
       <c r="AA4" s="2">
         <f t="shared" ref="AA4:AJ4" si="2">AA3-AA5</f>
-        <v>539808.63768000004</v>
+        <v>546195.36794999999</v>
       </c>
       <c r="AB4" s="2">
         <f t="shared" si="2"/>
-        <v>550604.8104336001</v>
+        <v>549691.01830488001</v>
       </c>
       <c r="AC4" s="2">
         <f t="shared" si="2"/>
-        <v>561616.90664227214</v>
+        <v>560684.83867097762</v>
       </c>
       <c r="AD4" s="2">
         <f t="shared" si="2"/>
-        <v>572849.24477511761</v>
+        <v>571898.53544439725</v>
       </c>
       <c r="AE4" s="2">
         <f t="shared" si="2"/>
-        <v>584306.22967061994</v>
+        <v>583336.50615328515</v>
       </c>
       <c r="AF4" s="2">
         <f t="shared" si="2"/>
-        <v>590149.29196732608</v>
+        <v>589169.87121481798</v>
       </c>
       <c r="AG4" s="2">
         <f t="shared" si="2"/>
-        <v>596050.7848869994</v>
+        <v>595061.5699269661</v>
       </c>
       <c r="AH4" s="2">
         <f t="shared" si="2"/>
-        <v>602011.29273586941</v>
+        <v>601012.18562623579</v>
       </c>
       <c r="AI4" s="2">
         <f t="shared" si="2"/>
-        <v>608031.40566322813</v>
+        <v>607022.30748249823</v>
       </c>
       <c r="AJ4" s="2">
         <f t="shared" si="2"/>
-        <v>614111.71971986035</v>
+        <v>613092.53055732313</v>
       </c>
     </row>
     <row r="5" spans="1:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1239,7 +1260,7 @@
         <v>13</v>
       </c>
       <c r="C5" s="7">
-        <f t="shared" ref="C5:N5" si="3">C3-C4</f>
+        <f t="shared" ref="C5:O5" si="3">C3-C4</f>
         <v>34722</v>
       </c>
       <c r="D5" s="7">
@@ -1286,77 +1307,89 @@
         <f t="shared" si="3"/>
         <v>44382</v>
       </c>
-      <c r="O5" s="7"/>
-      <c r="P5" s="7"/>
-      <c r="Q5" s="7"/>
-      <c r="R5" s="7"/>
+      <c r="O5" s="7">
+        <f t="shared" si="3"/>
+        <v>41306</v>
+      </c>
+      <c r="P5" s="7">
+        <f t="shared" ref="O5:P5" si="4">P3-P4</f>
+        <v>44631</v>
+      </c>
+      <c r="Q5" s="7">
+        <f>Q3*0.25</f>
+        <v>44516.85</v>
+      </c>
+      <c r="R5" s="7">
+        <f>R3*0.25</f>
+        <v>46492.654999999999</v>
+      </c>
       <c r="T5" s="7">
-        <f t="shared" ref="T5:Y5" si="4">T3-T4</f>
+        <f t="shared" ref="T5:Y5" si="5">T3-T4</f>
         <v>129359</v>
       </c>
       <c r="U5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>138836</v>
       </c>
       <c r="V5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>143754</v>
       </c>
       <c r="W5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>147568</v>
       </c>
       <c r="X5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>157983</v>
       </c>
       <c r="Y5" s="7">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>169232</v>
       </c>
       <c r="Z5" s="7">
         <f>Z3*0.25</f>
-        <v>177056.1</v>
+        <v>176762.255</v>
       </c>
       <c r="AA5" s="7">
-        <f>AA3*0.26</f>
-        <v>189662.49432000003</v>
+        <f>AA3*0.25</f>
+        <v>182065.12265</v>
       </c>
       <c r="AB5" s="7">
-        <f t="shared" ref="AB5:AJ5" si="5">AB3*0.26</f>
-        <v>193455.74420640004</v>
+        <f t="shared" ref="AB5:AJ5" si="6">AB3*0.26</f>
+        <v>193134.68210712002</v>
       </c>
       <c r="AC5" s="7">
-        <f t="shared" si="5"/>
-        <v>197324.85909052804</v>
+        <f t="shared" si="6"/>
+        <v>196997.3757492624</v>
       </c>
       <c r="AD5" s="7">
-        <f t="shared" si="5"/>
-        <v>201271.3562723386</v>
+        <f t="shared" si="6"/>
+        <v>200937.32326424768</v>
       </c>
       <c r="AE5" s="7">
-        <f t="shared" si="5"/>
-        <v>205296.78339778539</v>
+        <f t="shared" si="6"/>
+        <v>204956.06972953261</v>
       </c>
       <c r="AF5" s="7">
-        <f t="shared" si="5"/>
-        <v>207349.75123176325</v>
+        <f t="shared" si="6"/>
+        <v>207005.63042682793</v>
       </c>
       <c r="AG5" s="7">
-        <f t="shared" si="5"/>
-        <v>209423.24874408089</v>
+        <f t="shared" si="6"/>
+        <v>209075.68673109621</v>
       </c>
       <c r="AH5" s="7">
-        <f t="shared" si="5"/>
-        <v>211517.4812315217</v>
+        <f t="shared" si="6"/>
+        <v>211166.44359840718</v>
       </c>
       <c r="AI5" s="7">
-        <f t="shared" si="5"/>
-        <v>213632.65604383691</v>
+        <f t="shared" si="6"/>
+        <v>213278.10803439125</v>
       </c>
       <c r="AJ5" s="7">
-        <f t="shared" si="5"/>
-        <v>215768.98260427525</v>
+        <f t="shared" si="6"/>
+        <v>215410.88911473518</v>
       </c>
     </row>
     <row r="6" spans="1:156" x14ac:dyDescent="0.3">
@@ -1399,10 +1432,20 @@
       <c r="N6" s="2">
         <v>36523</v>
       </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
+      <c r="O6" s="2">
+        <v>34171</v>
+      </c>
+      <c r="P6" s="2">
+        <v>37345</v>
+      </c>
+      <c r="Q6" s="2">
+        <f>Q3*0.21</f>
+        <v>37394.153999999995</v>
+      </c>
+      <c r="R6" s="2">
+        <f>R3*0.21</f>
+        <v>39053.830199999997</v>
+      </c>
       <c r="T6" s="2">
         <v>108791</v>
       </c>
@@ -1424,49 +1467,49 @@
         <f>SUM(K6:N6)</f>
         <v>139884</v>
       </c>
-      <c r="Z6" s="2">
-        <f>Z3*0.2</f>
-        <v>141644.88</v>
+      <c r="Z6" s="12">
+        <f>SUM(O6:R6)</f>
+        <v>147963.98420000001</v>
       </c>
       <c r="AA6" s="2">
-        <f t="shared" ref="AA6:AJ6" si="6">AA3*0.2</f>
-        <v>145894.22640000001</v>
+        <f t="shared" ref="AA6:AJ6" si="7">AA3*0.2</f>
+        <v>145652.09812000001</v>
       </c>
       <c r="AB6" s="2">
-        <f t="shared" si="6"/>
-        <v>148812.11092800004</v>
+        <f t="shared" si="7"/>
+        <v>148565.14008240003</v>
       </c>
       <c r="AC6" s="2">
-        <f t="shared" si="6"/>
-        <v>151788.35314656002</v>
+        <f t="shared" si="7"/>
+        <v>151536.44288404801</v>
       </c>
       <c r="AD6" s="2">
-        <f t="shared" si="6"/>
-        <v>154824.12020949123</v>
+        <f t="shared" si="7"/>
+        <v>154567.17174172899</v>
       </c>
       <c r="AE6" s="2">
-        <f t="shared" si="6"/>
-        <v>157920.60261368108</v>
+        <f t="shared" si="7"/>
+        <v>157658.51517656355</v>
       </c>
       <c r="AF6" s="2">
-        <f t="shared" si="6"/>
-        <v>159499.80863981787</v>
+        <f t="shared" si="7"/>
+        <v>159235.10032832919</v>
       </c>
       <c r="AG6" s="2">
-        <f t="shared" si="6"/>
-        <v>161094.80672621608</v>
+        <f t="shared" si="7"/>
+        <v>160827.45133161248</v>
       </c>
       <c r="AH6" s="2">
-        <f t="shared" si="6"/>
-        <v>162705.75479347823</v>
+        <f t="shared" si="7"/>
+        <v>162435.72584492862</v>
       </c>
       <c r="AI6" s="2">
-        <f t="shared" si="6"/>
-        <v>164332.812341413</v>
+        <f t="shared" si="7"/>
+        <v>164060.0831033779</v>
       </c>
       <c r="AJ6" s="2">
-        <f t="shared" si="6"/>
-        <v>165976.14046482713</v>
+        <f t="shared" si="7"/>
+        <v>165700.68393441167</v>
       </c>
     </row>
     <row r="7" spans="1:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1475,124 +1518,136 @@
         <v>15</v>
       </c>
       <c r="C7" s="7">
-        <f t="shared" ref="C7:K7" si="7">C5-C6</f>
+        <f t="shared" ref="C7:K7" si="8">C5-C6</f>
         <v>5318</v>
       </c>
       <c r="D7" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6854</v>
       </c>
       <c r="E7" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2695</v>
       </c>
       <c r="F7" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>5561</v>
       </c>
       <c r="G7" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6240</v>
       </c>
       <c r="H7" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7316</v>
       </c>
       <c r="I7" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6202</v>
       </c>
       <c r="J7" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>7254</v>
       </c>
       <c r="K7" s="7">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>6841</v>
       </c>
       <c r="L7" s="7">
-        <f t="shared" ref="L7:N7" si="8">L5-L6</f>
+        <f t="shared" ref="L7:O7" si="9">L5-L6</f>
         <v>7940</v>
       </c>
       <c r="M7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>6708</v>
       </c>
       <c r="N7" s="7">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>7859</v>
       </c>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
-      <c r="Q7" s="7"/>
-      <c r="R7" s="7"/>
+      <c r="O7" s="7">
+        <f t="shared" si="9"/>
+        <v>7135</v>
+      </c>
+      <c r="P7" s="7">
+        <f t="shared" ref="O7:R7" si="10">P5-P6</f>
+        <v>7286</v>
+      </c>
+      <c r="Q7" s="7">
+        <f t="shared" si="10"/>
+        <v>7122.6960000000036</v>
+      </c>
+      <c r="R7" s="7">
+        <f t="shared" si="10"/>
+        <v>7438.8248000000021</v>
+      </c>
       <c r="T7" s="7">
-        <f t="shared" ref="T7:Z7" si="9">T5-T6</f>
+        <f t="shared" ref="T7:Z7" si="11">T5-T6</f>
         <v>20568</v>
       </c>
       <c r="U7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>22548</v>
       </c>
       <c r="V7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>25942</v>
       </c>
       <c r="W7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>20428</v>
       </c>
       <c r="X7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>27012</v>
       </c>
       <c r="Y7" s="7">
-        <f t="shared" si="9"/>
+        <f t="shared" si="11"/>
         <v>29348</v>
       </c>
       <c r="Z7" s="7">
-        <f t="shared" si="9"/>
-        <v>35411.22</v>
+        <f t="shared" si="11"/>
+        <v>28798.270799999998</v>
       </c>
       <c r="AA7" s="7">
-        <f t="shared" ref="AA7:AJ7" si="10">AA5-AA6</f>
-        <v>43768.267920000013</v>
+        <f t="shared" ref="AA7:AJ7" si="12">AA5-AA6</f>
+        <v>36413.024529999995</v>
       </c>
       <c r="AB7" s="7">
-        <f t="shared" si="10"/>
-        <v>44643.633278399997</v>
+        <f t="shared" si="12"/>
+        <v>44569.542024719995</v>
       </c>
       <c r="AC7" s="7">
-        <f t="shared" si="10"/>
-        <v>45536.505943968019</v>
+        <f t="shared" si="12"/>
+        <v>45460.932865214389</v>
       </c>
       <c r="AD7" s="7">
-        <f t="shared" si="10"/>
-        <v>46447.236062847369</v>
+        <f t="shared" si="12"/>
+        <v>46370.151522518689</v>
       </c>
       <c r="AE7" s="7">
-        <f t="shared" si="10"/>
-        <v>47376.180784104305</v>
+        <f t="shared" si="12"/>
+        <v>47297.554552969057</v>
       </c>
       <c r="AF7" s="7">
-        <f t="shared" si="10"/>
-        <v>47849.942591945379</v>
+        <f t="shared" si="12"/>
+        <v>47770.530098498741</v>
       </c>
       <c r="AG7" s="7">
-        <f t="shared" si="10"/>
-        <v>48328.442017864814</v>
+        <f t="shared" si="12"/>
+        <v>48248.235399483732</v>
       </c>
       <c r="AH7" s="7">
-        <f t="shared" si="10"/>
-        <v>48811.726438043464</v>
+        <f t="shared" si="12"/>
+        <v>48730.717753478559</v>
       </c>
       <c r="AI7" s="7">
-        <f t="shared" si="10"/>
-        <v>49299.84370242391</v>
+        <f t="shared" si="12"/>
+        <v>49218.024931013351</v>
       </c>
       <c r="AJ7" s="7">
-        <f t="shared" si="10"/>
-        <v>49792.842139448127</v>
+        <f t="shared" si="12"/>
+        <v>49710.205180323508</v>
       </c>
     </row>
     <row r="8" spans="1:156" x14ac:dyDescent="0.3">
@@ -1635,10 +1690,20 @@
       <c r="N8" s="2">
         <v>602</v>
       </c>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
+      <c r="O8" s="2">
+        <v>544</v>
+      </c>
+      <c r="P8" s="2">
+        <v>675</v>
+      </c>
+      <c r="Q8" s="2">
+        <f>M8*1.02</f>
+        <v>487.56</v>
+      </c>
+      <c r="R8" s="2">
+        <f>N8*1.02</f>
+        <v>614.04</v>
+      </c>
       <c r="T8" s="2">
         <v>2410</v>
       </c>
@@ -1660,49 +1725,49 @@
         <f>SUM(K8:N8)</f>
         <v>2245</v>
       </c>
-      <c r="Z8" s="2">
-        <f>Y8*1.01</f>
-        <v>2267.4499999999998</v>
+      <c r="Z8" s="12">
+        <f t="shared" ref="Z8:Z9" si="13">SUM(O8:R8)</f>
+        <v>2320.6</v>
       </c>
       <c r="AA8" s="2">
-        <f t="shared" ref="AA8:AJ8" si="11">Z8*1.01</f>
-        <v>2290.1244999999999</v>
+        <f t="shared" ref="AA8:AJ8" si="14">Z8*1.01</f>
+        <v>2343.806</v>
       </c>
       <c r="AB8" s="2">
-        <f t="shared" si="11"/>
-        <v>2313.0257449999999</v>
+        <f t="shared" si="14"/>
+        <v>2367.24406</v>
       </c>
       <c r="AC8" s="2">
-        <f t="shared" si="11"/>
-        <v>2336.15600245</v>
+        <f t="shared" si="14"/>
+        <v>2390.9165005999998</v>
       </c>
       <c r="AD8" s="2">
-        <f t="shared" si="11"/>
-        <v>2359.5175624744998</v>
+        <f t="shared" si="14"/>
+        <v>2414.8256656059998</v>
       </c>
       <c r="AE8" s="2">
-        <f t="shared" si="11"/>
-        <v>2383.1127380992448</v>
+        <f t="shared" si="14"/>
+        <v>2438.9739222620597</v>
       </c>
       <c r="AF8" s="2">
-        <f t="shared" si="11"/>
-        <v>2406.943865480237</v>
+        <f t="shared" si="14"/>
+        <v>2463.3636614846801</v>
       </c>
       <c r="AG8" s="2">
-        <f t="shared" si="11"/>
-        <v>2431.0133041350396</v>
+        <f t="shared" si="14"/>
+        <v>2487.9972980995267</v>
       </c>
       <c r="AH8" s="2">
-        <f t="shared" si="11"/>
-        <v>2455.3234371763901</v>
+        <f t="shared" si="14"/>
+        <v>2512.877271080522</v>
       </c>
       <c r="AI8" s="2">
-        <f t="shared" si="11"/>
-        <v>2479.8766715481543</v>
+        <f t="shared" si="14"/>
+        <v>2538.0060437913271</v>
       </c>
       <c r="AJ8" s="2">
-        <f t="shared" si="11"/>
-        <v>2504.6754382636359</v>
+        <f t="shared" si="14"/>
+        <v>2563.3861042292406</v>
       </c>
     </row>
     <row r="9" spans="1:156" x14ac:dyDescent="0.3">
@@ -1745,10 +1810,18 @@
       <c r="N9" s="2">
         <v>294</v>
       </c>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
+      <c r="O9" s="2">
+        <v>597</v>
+      </c>
+      <c r="P9" s="2">
+        <v>-2708</v>
+      </c>
+      <c r="Q9" s="2">
+        <v>0</v>
+      </c>
+      <c r="R9" s="2">
+        <v>0</v>
+      </c>
       <c r="T9" s="2">
         <v>-1958</v>
       </c>
@@ -1771,49 +1844,49 @@
         <f>SUM(K9:N9)</f>
         <v>794</v>
       </c>
-      <c r="Z9" s="2">
-        <f>Y9*1.01</f>
-        <v>801.94</v>
+      <c r="Z9" s="12">
+        <f t="shared" si="13"/>
+        <v>-2111</v>
       </c>
       <c r="AA9" s="2">
-        <f t="shared" ref="AA9:AJ9" si="12">Z9*1.01</f>
-        <v>809.95940000000007</v>
+        <f t="shared" ref="AA9:AJ9" si="15">Z9*1.01</f>
+        <v>-2132.11</v>
       </c>
       <c r="AB9" s="2">
-        <f t="shared" si="12"/>
-        <v>818.0589940000001</v>
+        <f t="shared" si="15"/>
+        <v>-2153.4311000000002</v>
       </c>
       <c r="AC9" s="2">
-        <f t="shared" si="12"/>
-        <v>826.2395839400001</v>
+        <f t="shared" si="15"/>
+        <v>-2174.9654110000001</v>
       </c>
       <c r="AD9" s="2">
-        <f t="shared" si="12"/>
-        <v>834.50197977940013</v>
+        <f t="shared" si="15"/>
+        <v>-2196.7150651100001</v>
       </c>
       <c r="AE9" s="2">
-        <f t="shared" si="12"/>
-        <v>842.84699957719408</v>
+        <f t="shared" si="15"/>
+        <v>-2218.6822157611</v>
       </c>
       <c r="AF9" s="2">
-        <f t="shared" si="12"/>
-        <v>851.27546957296602</v>
+        <f t="shared" si="15"/>
+        <v>-2240.869037918711</v>
       </c>
       <c r="AG9" s="2">
-        <f t="shared" si="12"/>
-        <v>859.78822426869567</v>
+        <f t="shared" si="15"/>
+        <v>-2263.2777282978982</v>
       </c>
       <c r="AH9" s="2">
-        <f t="shared" si="12"/>
-        <v>868.38610651138265</v>
+        <f t="shared" si="15"/>
+        <v>-2285.9105055808773</v>
       </c>
       <c r="AI9" s="2">
-        <f t="shared" si="12"/>
-        <v>877.06996757649654</v>
+        <f t="shared" si="15"/>
+        <v>-2308.7696106366861</v>
       </c>
       <c r="AJ9" s="2">
-        <f t="shared" si="12"/>
-        <v>885.84066725226148</v>
+        <f t="shared" si="15"/>
+        <v>-2331.857306743053</v>
       </c>
     </row>
     <row r="10" spans="1:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -1822,124 +1895,136 @@
         <v>18</v>
       </c>
       <c r="C10" s="7">
-        <f t="shared" ref="C10:K10" si="13">C7-C8-C9</f>
+        <f t="shared" ref="C10:K10" si="16">C7-C8-C9</f>
         <v>2901</v>
       </c>
       <c r="D10" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>6644</v>
       </c>
       <c r="E10" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>-1431</v>
       </c>
       <c r="F10" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>8902</v>
       </c>
       <c r="G10" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>2688</v>
       </c>
       <c r="H10" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>10727</v>
       </c>
       <c r="I10" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>915</v>
       </c>
       <c r="J10" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>7518</v>
       </c>
       <c r="K10" s="7">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>7035</v>
       </c>
       <c r="L10" s="7">
-        <f t="shared" ref="L10:N10" si="14">L7-L8-L9</f>
+        <f t="shared" ref="L10:O10" si="17">L7-L8-L9</f>
         <v>6213</v>
       </c>
       <c r="M10" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>6098</v>
       </c>
       <c r="N10" s="7">
-        <f t="shared" si="14"/>
+        <f t="shared" si="17"/>
         <v>6963</v>
       </c>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
-      <c r="Q10" s="7"/>
-      <c r="R10" s="7"/>
+      <c r="O10" s="7">
+        <f t="shared" si="17"/>
+        <v>5994</v>
+      </c>
+      <c r="P10" s="7">
+        <f t="shared" ref="O10:R10" si="18">P7-P8-P9</f>
+        <v>9319</v>
+      </c>
+      <c r="Q10" s="7">
+        <f t="shared" si="18"/>
+        <v>6635.1360000000032</v>
+      </c>
+      <c r="R10" s="7">
+        <f t="shared" si="18"/>
+        <v>6824.7848000000022</v>
+      </c>
       <c r="T10" s="7">
-        <f t="shared" ref="T10:Z10" si="15">T7-T8-T9</f>
+        <f t="shared" ref="T10:Z10" si="19">T7-T8-T9</f>
         <v>20116</v>
       </c>
       <c r="U10" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>20564</v>
       </c>
       <c r="V10" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>18696</v>
       </c>
       <c r="W10" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>17016</v>
       </c>
       <c r="X10" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>21848</v>
       </c>
       <c r="Y10" s="7">
-        <f t="shared" si="15"/>
+        <f t="shared" si="19"/>
         <v>26309</v>
       </c>
       <c r="Z10" s="7">
-        <f t="shared" si="15"/>
-        <v>32341.830000000005</v>
+        <f t="shared" si="19"/>
+        <v>28588.6708</v>
       </c>
       <c r="AA10" s="7">
-        <f t="shared" ref="AA10:AJ10" si="16">AA7-AA8-AA9</f>
-        <v>40668.184020000015</v>
+        <f t="shared" ref="AA10:AJ10" si="20">AA7-AA8-AA9</f>
+        <v>36201.328529999999</v>
       </c>
       <c r="AB10" s="7">
-        <f t="shared" si="16"/>
-        <v>41512.548539399999</v>
+        <f t="shared" si="20"/>
+        <v>44355.729064719999</v>
       </c>
       <c r="AC10" s="7">
-        <f t="shared" si="16"/>
-        <v>42374.110357578022</v>
+        <f t="shared" si="20"/>
+        <v>45244.981775614389</v>
       </c>
       <c r="AD10" s="7">
-        <f t="shared" si="16"/>
-        <v>43253.216520593465</v>
+        <f t="shared" si="20"/>
+        <v>46152.040922022694</v>
       </c>
       <c r="AE10" s="7">
-        <f t="shared" si="16"/>
-        <v>44150.221046427861</v>
+        <f t="shared" si="20"/>
+        <v>47077.262846468097</v>
       </c>
       <c r="AF10" s="7">
-        <f t="shared" si="16"/>
-        <v>44591.723256892175</v>
+        <f t="shared" si="20"/>
+        <v>47548.035474932774</v>
       </c>
       <c r="AG10" s="7">
-        <f t="shared" si="16"/>
-        <v>45037.640489461075</v>
+        <f t="shared" si="20"/>
+        <v>48023.515829682103</v>
       </c>
       <c r="AH10" s="7">
-        <f t="shared" si="16"/>
-        <v>45488.016894355693</v>
+        <f t="shared" si="20"/>
+        <v>48503.750987978914</v>
       </c>
       <c r="AI10" s="7">
-        <f t="shared" si="16"/>
-        <v>45942.897063299257</v>
+        <f t="shared" si="20"/>
+        <v>48988.78849785871</v>
       </c>
       <c r="AJ10" s="7">
-        <f t="shared" si="16"/>
-        <v>46402.32603393223</v>
+        <f t="shared" si="20"/>
+        <v>49478.676382837322</v>
       </c>
     </row>
     <row r="11" spans="1:156" x14ac:dyDescent="0.3">
@@ -1982,10 +2067,20 @@
       <c r="N11" s="2">
         <v>1538</v>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
+      <c r="O11" s="2">
+        <v>1355</v>
+      </c>
+      <c r="P11" s="2">
+        <v>2168</v>
+      </c>
+      <c r="Q11" s="2">
+        <f>Q10*0.23</f>
+        <v>1526.0812800000008</v>
+      </c>
+      <c r="R11" s="2">
+        <f>R10*0.23</f>
+        <v>1569.7005040000006</v>
+      </c>
       <c r="T11" s="2">
         <v>4915</v>
       </c>
@@ -2007,49 +2102,49 @@
         <f>SUM(K11:N11)</f>
         <v>6152</v>
       </c>
-      <c r="Z11" s="2">
-        <f>Z10*0.25</f>
-        <v>8085.4575000000013</v>
+      <c r="Z11" s="12">
+        <f t="shared" ref="Z11:Z12" si="21">SUM(O11:R11)</f>
+        <v>6618.7817840000007</v>
       </c>
       <c r="AA11" s="2">
-        <f t="shared" ref="AA11:AJ11" si="17">AA10*0.25</f>
-        <v>10167.046005000004</v>
+        <f t="shared" ref="AA11:AJ11" si="22">AA10*0.25</f>
+        <v>9050.3321324999997</v>
       </c>
       <c r="AB11" s="2">
-        <f t="shared" si="17"/>
-        <v>10378.13713485</v>
+        <f t="shared" si="22"/>
+        <v>11088.93226618</v>
       </c>
       <c r="AC11" s="2">
-        <f t="shared" si="17"/>
-        <v>10593.527589394505</v>
+        <f t="shared" si="22"/>
+        <v>11311.245443903597</v>
       </c>
       <c r="AD11" s="2">
-        <f t="shared" si="17"/>
-        <v>10813.304130148366</v>
+        <f t="shared" si="22"/>
+        <v>11538.010230505673</v>
       </c>
       <c r="AE11" s="2">
-        <f t="shared" si="17"/>
-        <v>11037.555261606965</v>
+        <f t="shared" si="22"/>
+        <v>11769.315711617024</v>
       </c>
       <c r="AF11" s="2">
-        <f t="shared" si="17"/>
-        <v>11147.930814223044</v>
+        <f t="shared" si="22"/>
+        <v>11887.008868733194</v>
       </c>
       <c r="AG11" s="2">
-        <f t="shared" si="17"/>
-        <v>11259.410122365269</v>
+        <f t="shared" si="22"/>
+        <v>12005.878957420526</v>
       </c>
       <c r="AH11" s="2">
-        <f t="shared" si="17"/>
-        <v>11372.004223588923</v>
+        <f t="shared" si="22"/>
+        <v>12125.937746994729</v>
       </c>
       <c r="AI11" s="2">
-        <f t="shared" si="17"/>
-        <v>11485.724265824814</v>
+        <f t="shared" si="22"/>
+        <v>12247.197124464677</v>
       </c>
       <c r="AJ11" s="2">
-        <f t="shared" si="17"/>
-        <v>11600.581508483057</v>
+        <f t="shared" si="22"/>
+        <v>12369.669095709331</v>
       </c>
     </row>
     <row r="12" spans="1:156" x14ac:dyDescent="0.3">
@@ -2092,10 +2187,20 @@
       <c r="N12" s="2">
         <v>171</v>
       </c>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
+      <c r="O12" s="2">
+        <v>152</v>
+      </c>
+      <c r="P12" s="2">
+        <v>125</v>
+      </c>
+      <c r="Q12" s="2">
+        <f>Q3*0.001</f>
+        <v>178.06739999999999</v>
+      </c>
+      <c r="R12" s="2">
+        <f>R3*0.001</f>
+        <v>185.97062</v>
+      </c>
       <c r="T12" s="2">
         <v>320</v>
       </c>
@@ -2117,49 +2222,49 @@
         <f>SUM(K12:N12)</f>
         <v>721</v>
       </c>
-      <c r="Z12" s="2">
-        <f>Z3*0.001</f>
-        <v>708.22440000000006</v>
+      <c r="Z12" s="12">
+        <f t="shared" si="21"/>
+        <v>641.03801999999996</v>
       </c>
       <c r="AA12" s="2">
-        <f t="shared" ref="AA12:AJ12" si="18">AA3*0.001</f>
-        <v>729.47113200000013</v>
+        <f t="shared" ref="AA12:AJ12" si="23">AA3*0.001</f>
+        <v>728.26049060000003</v>
       </c>
       <c r="AB12" s="2">
-        <f t="shared" si="18"/>
-        <v>744.06055464000008</v>
+        <f t="shared" si="23"/>
+        <v>742.82570041200006</v>
       </c>
       <c r="AC12" s="2">
-        <f t="shared" si="18"/>
-        <v>758.94176573280015</v>
+        <f t="shared" si="23"/>
+        <v>757.68221442024003</v>
       </c>
       <c r="AD12" s="2">
-        <f t="shared" si="18"/>
-        <v>774.12060104745615</v>
+        <f t="shared" si="23"/>
+        <v>772.83585870864488</v>
       </c>
       <c r="AE12" s="2">
-        <f t="shared" si="18"/>
-        <v>789.60301306840529</v>
+        <f t="shared" si="23"/>
+        <v>788.2925758828178</v>
       </c>
       <c r="AF12" s="2">
-        <f t="shared" si="18"/>
-        <v>797.49904319908933</v>
+        <f t="shared" si="23"/>
+        <v>796.17550164164595</v>
       </c>
       <c r="AG12" s="2">
-        <f t="shared" si="18"/>
-        <v>805.47403363108026</v>
+        <f t="shared" si="23"/>
+        <v>804.13725665806237</v>
       </c>
       <c r="AH12" s="2">
-        <f t="shared" si="18"/>
-        <v>813.52877396739109</v>
+        <f t="shared" si="23"/>
+        <v>812.17862922464303</v>
       </c>
       <c r="AI12" s="2">
-        <f t="shared" si="18"/>
-        <v>821.664061707065</v>
+        <f t="shared" si="23"/>
+        <v>820.30041551688942</v>
       </c>
       <c r="AJ12" s="2">
-        <f t="shared" si="18"/>
-        <v>829.88070232413554</v>
+        <f t="shared" si="23"/>
+        <v>828.50341967205839</v>
       </c>
     </row>
     <row r="13" spans="1:156" s="1" customFormat="1" x14ac:dyDescent="0.3">
@@ -2168,604 +2273,616 @@
         <v>20</v>
       </c>
       <c r="C13" s="7">
-        <f t="shared" ref="C13:K13" si="19">C10-C11-C12</f>
+        <f t="shared" ref="C13:K13" si="24">C10-C11-C12</f>
         <v>2054</v>
       </c>
       <c r="D13" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>5149</v>
       </c>
       <c r="E13" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>-1798</v>
       </c>
       <c r="F13" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>6275</v>
       </c>
       <c r="G13" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>1673</v>
       </c>
       <c r="H13" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>7891</v>
       </c>
       <c r="I13" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>453</v>
       </c>
       <c r="J13" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>5494</v>
       </c>
       <c r="K13" s="7">
-        <f t="shared" si="19"/>
+        <f t="shared" si="24"/>
         <v>5104</v>
       </c>
       <c r="L13" s="7">
-        <f t="shared" ref="L13:N13" si="20">L10-L11-L12</f>
+        <f t="shared" ref="L13:O13" si="25">L10-L11-L12</f>
         <v>4501</v>
       </c>
       <c r="M13" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>4577</v>
       </c>
       <c r="N13" s="7">
-        <f t="shared" si="20"/>
+        <f t="shared" si="25"/>
         <v>5254</v>
       </c>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="7"/>
-      <c r="R13" s="7"/>
+      <c r="O13" s="7">
+        <f t="shared" si="25"/>
+        <v>4487</v>
+      </c>
+      <c r="P13" s="7">
+        <f t="shared" ref="O13:P13" si="26">P10-P11-P12</f>
+        <v>7026</v>
+      </c>
+      <c r="Q13" s="7">
+        <f t="shared" ref="Q13:R13" si="27">Q10-Q11-Q12</f>
+        <v>4930.987320000002</v>
+      </c>
+      <c r="R13" s="7">
+        <f t="shared" si="27"/>
+        <v>5069.1136760000018</v>
+      </c>
       <c r="T13" s="7">
-        <f t="shared" ref="T13:Z13" si="21">T10-T11-T12</f>
+        <f t="shared" ref="T13:Z13" si="28">T10-T11-T12</f>
         <v>14881</v>
       </c>
       <c r="U13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>13510</v>
       </c>
       <c r="V13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>13673</v>
       </c>
       <c r="W13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>11680</v>
       </c>
       <c r="X13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>15511</v>
       </c>
       <c r="Y13" s="7">
-        <f t="shared" si="21"/>
+        <f t="shared" si="28"/>
         <v>19436</v>
       </c>
       <c r="Z13" s="7">
-        <f t="shared" si="21"/>
-        <v>23548.148100000006</v>
+        <f t="shared" si="28"/>
+        <v>21328.850996000001</v>
       </c>
       <c r="AA13" s="7">
-        <f t="shared" ref="AA13:AJ13" si="22">AA10-AA11-AA12</f>
-        <v>29771.666883000013</v>
+        <f t="shared" ref="AA13:AJ13" si="29">AA10-AA11-AA12</f>
+        <v>26422.735906899998</v>
       </c>
       <c r="AB13" s="7">
-        <f t="shared" si="22"/>
-        <v>30390.350849909999</v>
+        <f t="shared" si="29"/>
+        <v>32523.971098128004</v>
       </c>
       <c r="AC13" s="7">
-        <f t="shared" si="22"/>
-        <v>31021.641002450713</v>
+        <f t="shared" si="29"/>
+        <v>33176.054117290558</v>
       </c>
       <c r="AD13" s="7">
-        <f t="shared" si="22"/>
-        <v>31665.791789397641</v>
+        <f t="shared" si="29"/>
+        <v>33841.194832808374</v>
       </c>
       <c r="AE13" s="7">
-        <f t="shared" si="22"/>
-        <v>32323.062771752495</v>
+        <f t="shared" si="29"/>
+        <v>34519.65455896825</v>
       </c>
       <c r="AF13" s="7">
-        <f t="shared" si="22"/>
-        <v>32646.293399470043</v>
+        <f t="shared" si="29"/>
+        <v>34864.851104557936</v>
       </c>
       <c r="AG13" s="7">
-        <f t="shared" si="22"/>
-        <v>32972.756333464728</v>
+        <f t="shared" si="29"/>
+        <v>35213.499615603512</v>
       </c>
       <c r="AH13" s="7">
-        <f t="shared" si="22"/>
-        <v>33302.483896799378</v>
+        <f t="shared" si="29"/>
+        <v>35565.634611759546</v>
       </c>
       <c r="AI13" s="7">
-        <f t="shared" si="22"/>
-        <v>33635.508735767376</v>
+        <f t="shared" si="29"/>
+        <v>35921.290957877143</v>
       </c>
       <c r="AJ13" s="7">
-        <f t="shared" si="22"/>
-        <v>33971.863823125037</v>
+        <f t="shared" si="29"/>
+        <v>36280.503867455933</v>
       </c>
       <c r="AK13" s="1">
         <f>AJ13*(1+$AM$18)</f>
-        <v>33632.145184893787</v>
+        <v>35917.698828781373</v>
       </c>
       <c r="AL13" s="1">
-        <f t="shared" ref="AL13:CW13" si="23">AK13*(1+$AM$18)</f>
-        <v>33295.823733044846</v>
+        <f t="shared" ref="AL13:CW13" si="30">AK13*(1+$AM$18)</f>
+        <v>35558.521840493559</v>
       </c>
       <c r="AM13" s="1">
-        <f t="shared" si="23"/>
-        <v>32962.865495714395</v>
+        <f t="shared" si="30"/>
+        <v>35202.936622088622</v>
       </c>
       <c r="AN13" s="1">
-        <f t="shared" si="23"/>
-        <v>32633.23684075725</v>
+        <f t="shared" si="30"/>
+        <v>34850.907255867736</v>
       </c>
       <c r="AO13" s="1">
-        <f t="shared" si="23"/>
-        <v>32306.904472349677</v>
+        <f t="shared" si="30"/>
+        <v>34502.398183309058</v>
       </c>
       <c r="AP13" s="1">
-        <f t="shared" si="23"/>
-        <v>31983.835427626182</v>
+        <f t="shared" si="30"/>
+        <v>34157.37420147597</v>
       </c>
       <c r="AQ13" s="1">
-        <f t="shared" si="23"/>
-        <v>31663.997073349921</v>
+        <f t="shared" si="30"/>
+        <v>33815.800459461207</v>
       </c>
       <c r="AR13" s="1">
-        <f t="shared" si="23"/>
-        <v>31347.357102616421</v>
+        <f t="shared" si="30"/>
+        <v>33477.642454866596</v>
       </c>
       <c r="AS13" s="1">
-        <f t="shared" si="23"/>
-        <v>31033.883531590258</v>
+        <f t="shared" si="30"/>
+        <v>33142.866030317928</v>
       </c>
       <c r="AT13" s="1">
-        <f t="shared" si="23"/>
-        <v>30723.544696274355</v>
+        <f t="shared" si="30"/>
+        <v>32811.437370014748</v>
       </c>
       <c r="AU13" s="1">
-        <f t="shared" si="23"/>
-        <v>30416.309249311613</v>
+        <f t="shared" si="30"/>
+        <v>32483.3229963146</v>
       </c>
       <c r="AV13" s="1">
-        <f t="shared" si="23"/>
-        <v>30112.146156818497</v>
+        <f t="shared" si="30"/>
+        <v>32158.489766351453</v>
       </c>
       <c r="AW13" s="1">
-        <f t="shared" si="23"/>
-        <v>29811.024695250311</v>
+        <f t="shared" si="30"/>
+        <v>31836.90486868794</v>
       </c>
       <c r="AX13" s="1">
-        <f t="shared" si="23"/>
-        <v>29512.914448297808</v>
+        <f t="shared" si="30"/>
+        <v>31518.53582000106</v>
       </c>
       <c r="AY13" s="1">
-        <f t="shared" si="23"/>
-        <v>29217.785303814831</v>
+        <f t="shared" si="30"/>
+        <v>31203.350461801048</v>
       </c>
       <c r="AZ13" s="1">
-        <f t="shared" si="23"/>
-        <v>28925.607450776683</v>
+        <f t="shared" si="30"/>
+        <v>30891.316957183037</v>
       </c>
       <c r="BA13" s="1">
-        <f t="shared" si="23"/>
-        <v>28636.351376268914</v>
+        <f t="shared" si="30"/>
+        <v>30582.403787611205</v>
       </c>
       <c r="BB13" s="1">
-        <f t="shared" si="23"/>
-        <v>28349.987862506227</v>
+        <f t="shared" si="30"/>
+        <v>30276.579749735094</v>
       </c>
       <c r="BC13" s="1">
-        <f t="shared" si="23"/>
-        <v>28066.487983881165</v>
+        <f t="shared" si="30"/>
+        <v>29973.813952237742</v>
       </c>
       <c r="BD13" s="1">
-        <f t="shared" si="23"/>
-        <v>27785.823104042352</v>
+        <f t="shared" si="30"/>
+        <v>29674.075812715364</v>
       </c>
       <c r="BE13" s="1">
-        <f t="shared" si="23"/>
-        <v>27507.964873001929</v>
+        <f t="shared" si="30"/>
+        <v>29377.335054588209</v>
       </c>
       <c r="BF13" s="1">
-        <f t="shared" si="23"/>
-        <v>27232.885224271908</v>
+        <f t="shared" si="30"/>
+        <v>29083.561704042328</v>
       </c>
       <c r="BG13" s="1">
-        <f t="shared" si="23"/>
-        <v>26960.556372029187</v>
+        <f t="shared" si="30"/>
+        <v>28792.726087001905</v>
       </c>
       <c r="BH13" s="1">
-        <f t="shared" si="23"/>
-        <v>26690.950808308895</v>
+        <f t="shared" si="30"/>
+        <v>28504.798826131886</v>
       </c>
       <c r="BI13" s="1">
-        <f t="shared" si="23"/>
-        <v>26424.041300225806</v>
+        <f t="shared" si="30"/>
+        <v>28219.750837870568</v>
       </c>
       <c r="BJ13" s="1">
-        <f t="shared" si="23"/>
-        <v>26159.800887223548</v>
+        <f t="shared" si="30"/>
+        <v>27937.55332949186</v>
       </c>
       <c r="BK13" s="1">
-        <f t="shared" si="23"/>
-        <v>25898.202878351312</v>
+        <f t="shared" si="30"/>
+        <v>27658.177796196942</v>
       </c>
       <c r="BL13" s="1">
-        <f t="shared" si="23"/>
-        <v>25639.220849567799</v>
+        <f t="shared" si="30"/>
+        <v>27381.596018234974</v>
       </c>
       <c r="BM13" s="1">
-        <f t="shared" si="23"/>
-        <v>25382.828641072119</v>
+        <f t="shared" si="30"/>
+        <v>27107.780058052624</v>
       </c>
       <c r="BN13" s="1">
-        <f t="shared" si="23"/>
-        <v>25129.000354661399</v>
+        <f t="shared" si="30"/>
+        <v>26836.702257472098</v>
       </c>
       <c r="BO13" s="1">
-        <f t="shared" si="23"/>
-        <v>24877.710351114783</v>
+        <f t="shared" si="30"/>
+        <v>26568.335234897375</v>
       </c>
       <c r="BP13" s="1">
-        <f t="shared" si="23"/>
-        <v>24628.933247603636</v>
+        <f t="shared" si="30"/>
+        <v>26302.651882548402</v>
       </c>
       <c r="BQ13" s="1">
-        <f t="shared" si="23"/>
-        <v>24382.643915127599</v>
+        <f t="shared" si="30"/>
+        <v>26039.625363722917</v>
       </c>
       <c r="BR13" s="1">
-        <f t="shared" si="23"/>
-        <v>24138.817475976324</v>
+        <f t="shared" si="30"/>
+        <v>25779.229110085686</v>
       </c>
       <c r="BS13" s="1">
-        <f t="shared" si="23"/>
-        <v>23897.429301216562</v>
+        <f t="shared" si="30"/>
+        <v>25521.436818984828</v>
       </c>
       <c r="BT13" s="1">
-        <f t="shared" si="23"/>
-        <v>23658.455008204397</v>
+        <f t="shared" si="30"/>
+        <v>25266.22245079498</v>
       </c>
       <c r="BU13" s="1">
-        <f t="shared" si="23"/>
-        <v>23421.870458122354</v>
+        <f t="shared" si="30"/>
+        <v>25013.560226287031</v>
       </c>
       <c r="BV13" s="1">
-        <f t="shared" si="23"/>
-        <v>23187.651753541129</v>
+        <f t="shared" si="30"/>
+        <v>24763.424624024159</v>
       </c>
       <c r="BW13" s="1">
-        <f t="shared" si="23"/>
-        <v>22955.775236005717</v>
+        <f t="shared" si="30"/>
+        <v>24515.790377783916</v>
       </c>
       <c r="BX13" s="1">
-        <f t="shared" si="23"/>
-        <v>22726.217483645658</v>
+        <f t="shared" si="30"/>
+        <v>24270.632474006077</v>
       </c>
       <c r="BY13" s="1">
-        <f t="shared" si="23"/>
-        <v>22498.9553088092</v>
+        <f t="shared" si="30"/>
+        <v>24027.926149266015</v>
       </c>
       <c r="BZ13" s="1">
-        <f t="shared" si="23"/>
-        <v>22273.965755721107</v>
+        <f t="shared" si="30"/>
+        <v>23787.646887773353</v>
       </c>
       <c r="CA13" s="1">
-        <f t="shared" si="23"/>
-        <v>22051.226098163894</v>
+        <f t="shared" si="30"/>
+        <v>23549.77041889562</v>
       </c>
       <c r="CB13" s="1">
-        <f t="shared" si="23"/>
-        <v>21830.713837182255</v>
+        <f t="shared" si="30"/>
+        <v>23314.272714706662</v>
       </c>
       <c r="CC13" s="1">
-        <f t="shared" si="23"/>
-        <v>21612.406698810431</v>
+        <f t="shared" si="30"/>
+        <v>23081.129987559594</v>
       </c>
       <c r="CD13" s="1">
-        <f t="shared" si="23"/>
-        <v>21396.282631822327</v>
+        <f t="shared" si="30"/>
+        <v>22850.318687683997</v>
       </c>
       <c r="CE13" s="1">
-        <f t="shared" si="23"/>
-        <v>21182.319805504103</v>
+        <f t="shared" si="30"/>
+        <v>22621.815500807155</v>
       </c>
       <c r="CF13" s="1">
-        <f t="shared" si="23"/>
-        <v>20970.496607449062</v>
+        <f t="shared" si="30"/>
+        <v>22395.597345799084</v>
       </c>
       <c r="CG13" s="1">
-        <f t="shared" si="23"/>
-        <v>20760.79164137457</v>
+        <f t="shared" si="30"/>
+        <v>22171.641372341091</v>
       </c>
       <c r="CH13" s="1">
-        <f t="shared" si="23"/>
-        <v>20553.183724960825</v>
+        <f t="shared" si="30"/>
+        <v>21949.924958617681</v>
       </c>
       <c r="CI13" s="1">
-        <f t="shared" si="23"/>
-        <v>20347.651887711218</v>
+        <f t="shared" si="30"/>
+        <v>21730.425709031504</v>
       </c>
       <c r="CJ13" s="1">
-        <f t="shared" si="23"/>
-        <v>20144.175368834105</v>
+        <f t="shared" si="30"/>
+        <v>21513.121451941188</v>
       </c>
       <c r="CK13" s="1">
-        <f t="shared" si="23"/>
-        <v>19942.733615145764</v>
+        <f t="shared" si="30"/>
+        <v>21297.990237421775</v>
       </c>
       <c r="CL13" s="1">
-        <f t="shared" si="23"/>
-        <v>19743.306278994307</v>
+        <f t="shared" si="30"/>
+        <v>21085.010335047558</v>
       </c>
       <c r="CM13" s="1">
-        <f t="shared" si="23"/>
-        <v>19545.873216204363</v>
+        <f t="shared" si="30"/>
+        <v>20874.160231697082</v>
       </c>
       <c r="CN13" s="1">
-        <f t="shared" si="23"/>
-        <v>19350.414484042321</v>
+        <f t="shared" si="30"/>
+        <v>20665.41862938011</v>
       </c>
       <c r="CO13" s="1">
-        <f t="shared" si="23"/>
-        <v>19156.910339201899</v>
+        <f t="shared" si="30"/>
+        <v>20458.764443086307</v>
       </c>
       <c r="CP13" s="1">
-        <f t="shared" si="23"/>
-        <v>18965.341235809879</v>
+        <f t="shared" si="30"/>
+        <v>20254.176798655444</v>
       </c>
       <c r="CQ13" s="1">
-        <f t="shared" si="23"/>
-        <v>18775.687823451779</v>
+        <f t="shared" si="30"/>
+        <v>20051.635030668891</v>
       </c>
       <c r="CR13" s="1">
-        <f t="shared" si="23"/>
-        <v>18587.93094521726</v>
+        <f t="shared" si="30"/>
+        <v>19851.1186803622</v>
       </c>
       <c r="CS13" s="1">
-        <f t="shared" si="23"/>
-        <v>18402.051635765089</v>
+        <f t="shared" si="30"/>
+        <v>19652.607493558578</v>
       </c>
       <c r="CT13" s="1">
-        <f t="shared" si="23"/>
-        <v>18218.031119407438</v>
+        <f t="shared" si="30"/>
+        <v>19456.081418622991</v>
       </c>
       <c r="CU13" s="1">
-        <f t="shared" si="23"/>
-        <v>18035.850808213363</v>
+        <f t="shared" si="30"/>
+        <v>19261.520604436762</v>
       </c>
       <c r="CV13" s="1">
-        <f t="shared" si="23"/>
-        <v>17855.492300131231</v>
+        <f t="shared" si="30"/>
+        <v>19068.905398392395</v>
       </c>
       <c r="CW13" s="1">
-        <f t="shared" si="23"/>
-        <v>17676.937377129918</v>
+        <f t="shared" si="30"/>
+        <v>18878.216344408473</v>
       </c>
       <c r="CX13" s="1">
-        <f t="shared" ref="CX13:EZ13" si="24">CW13*(1+$AM$18)</f>
-        <v>17500.16800335862</v>
+        <f t="shared" ref="CX13:EZ13" si="31">CW13*(1+$AM$18)</f>
+        <v>18689.434180964388</v>
       </c>
       <c r="CY13" s="1">
-        <f t="shared" si="24"/>
-        <v>17325.166323325033</v>
+        <f t="shared" si="31"/>
+        <v>18502.539839154746</v>
       </c>
       <c r="CZ13" s="1">
-        <f t="shared" si="24"/>
-        <v>17151.914660091781</v>
+        <f t="shared" si="31"/>
+        <v>18317.5144407632</v>
       </c>
       <c r="DA13" s="1">
-        <f t="shared" si="24"/>
-        <v>16980.395513490865</v>
+        <f t="shared" si="31"/>
+        <v>18134.339296355567</v>
       </c>
       <c r="DB13" s="1">
-        <f t="shared" si="24"/>
-        <v>16810.591558355954</v>
+        <f t="shared" si="31"/>
+        <v>17952.995903392009</v>
       </c>
       <c r="DC13" s="1">
-        <f t="shared" si="24"/>
-        <v>16642.485642772393</v>
+        <f t="shared" si="31"/>
+        <v>17773.465944358089</v>
       </c>
       <c r="DD13" s="1">
-        <f t="shared" si="24"/>
-        <v>16476.060786344668</v>
+        <f t="shared" si="31"/>
+        <v>17595.731284914509</v>
       </c>
       <c r="DE13" s="1">
-        <f t="shared" si="24"/>
-        <v>16311.30017848122</v>
+        <f t="shared" si="31"/>
+        <v>17419.773972065363</v>
       </c>
       <c r="DF13" s="1">
-        <f t="shared" si="24"/>
-        <v>16148.187176696409</v>
+        <f t="shared" si="31"/>
+        <v>17245.576232344709</v>
       </c>
       <c r="DG13" s="1">
-        <f t="shared" si="24"/>
-        <v>15986.705304929445</v>
+        <f t="shared" si="31"/>
+        <v>17073.120470021262</v>
       </c>
       <c r="DH13" s="1">
-        <f t="shared" si="24"/>
-        <v>15826.83825188015</v>
+        <f t="shared" si="31"/>
+        <v>16902.38926532105</v>
       </c>
       <c r="DI13" s="1">
-        <f t="shared" si="24"/>
-        <v>15668.569869361349</v>
+        <f t="shared" si="31"/>
+        <v>16733.365372667839</v>
       </c>
       <c r="DJ13" s="1">
-        <f t="shared" si="24"/>
-        <v>15511.884170667736</v>
+        <f t="shared" si="31"/>
+        <v>16566.031718941162</v>
       </c>
       <c r="DK13" s="1">
-        <f t="shared" si="24"/>
-        <v>15356.765328961059</v>
+        <f t="shared" si="31"/>
+        <v>16400.371401751749</v>
       </c>
       <c r="DL13" s="1">
-        <f t="shared" si="24"/>
-        <v>15203.197675671448</v>
+        <f t="shared" si="31"/>
+        <v>16236.367687734231</v>
       </c>
       <c r="DM13" s="1">
-        <f t="shared" si="24"/>
-        <v>15051.165698914734</v>
+        <f t="shared" si="31"/>
+        <v>16074.004010856888</v>
       </c>
       <c r="DN13" s="1">
-        <f t="shared" si="24"/>
-        <v>14900.654041925587</v>
+        <f t="shared" si="31"/>
+        <v>15913.263970748319</v>
       </c>
       <c r="DO13" s="1">
-        <f t="shared" si="24"/>
-        <v>14751.647501506332</v>
+        <f t="shared" si="31"/>
+        <v>15754.131331040837</v>
       </c>
       <c r="DP13" s="1">
-        <f t="shared" si="24"/>
-        <v>14604.131026491268</v>
+        <f t="shared" si="31"/>
+        <v>15596.590017730428</v>
       </c>
       <c r="DQ13" s="1">
-        <f t="shared" si="24"/>
-        <v>14458.089716226355</v>
+        <f t="shared" si="31"/>
+        <v>15440.624117553123</v>
       </c>
       <c r="DR13" s="1">
-        <f t="shared" si="24"/>
-        <v>14313.508819064091</v>
+        <f t="shared" si="31"/>
+        <v>15286.217876377592</v>
       </c>
       <c r="DS13" s="1">
-        <f t="shared" si="24"/>
-        <v>14170.373730873449</v>
+        <f t="shared" si="31"/>
+        <v>15133.355697613815</v>
       </c>
       <c r="DT13" s="1">
-        <f t="shared" si="24"/>
-        <v>14028.669993564714</v>
+        <f t="shared" si="31"/>
+        <v>14982.022140637677</v>
       </c>
       <c r="DU13" s="1">
-        <f t="shared" si="24"/>
-        <v>13888.383293629067</v>
+        <f t="shared" si="31"/>
+        <v>14832.2019192313</v>
       </c>
       <c r="DV13" s="1">
-        <f t="shared" si="24"/>
-        <v>13749.499460692776</v>
+        <f t="shared" si="31"/>
+        <v>14683.879900038986</v>
       </c>
       <c r="DW13" s="1">
-        <f t="shared" si="24"/>
-        <v>13612.004466085848</v>
+        <f t="shared" si="31"/>
+        <v>14537.041101038596</v>
       </c>
       <c r="DX13" s="1">
-        <f t="shared" si="24"/>
-        <v>13475.884421424989</v>
+        <f t="shared" si="31"/>
+        <v>14391.67069002821</v>
       </c>
       <c r="DY13" s="1">
-        <f t="shared" si="24"/>
-        <v>13341.12557721074</v>
+        <f t="shared" si="31"/>
+        <v>14247.753983127928</v>
       </c>
       <c r="DZ13" s="1">
-        <f t="shared" si="24"/>
-        <v>13207.714321438632</v>
+        <f t="shared" si="31"/>
+        <v>14105.276443296649</v>
       </c>
       <c r="EA13" s="1">
-        <f t="shared" si="24"/>
-        <v>13075.637178224246</v>
+        <f t="shared" si="31"/>
+        <v>13964.223678863682</v>
       </c>
       <c r="EB13" s="1">
-        <f t="shared" si="24"/>
-        <v>12944.880806442003</v>
+        <f t="shared" si="31"/>
+        <v>13824.581442075045</v>
       </c>
       <c r="EC13" s="1">
-        <f t="shared" si="24"/>
-        <v>12815.431998377582</v>
+        <f t="shared" si="31"/>
+        <v>13686.335627654295</v>
       </c>
       <c r="ED13" s="1">
-        <f t="shared" si="24"/>
-        <v>12687.277678393806</v>
+        <f t="shared" si="31"/>
+        <v>13549.472271377752</v>
       </c>
       <c r="EE13" s="1">
-        <f t="shared" si="24"/>
-        <v>12560.404901609869</v>
+        <f t="shared" si="31"/>
+        <v>13413.977548663974</v>
       </c>
       <c r="EF13" s="1">
-        <f t="shared" si="24"/>
-        <v>12434.800852593769</v>
+        <f t="shared" si="31"/>
+        <v>13279.837773177334</v>
       </c>
       <c r="EG13" s="1">
-        <f t="shared" si="24"/>
-        <v>12310.452844067831</v>
+        <f t="shared" si="31"/>
+        <v>13147.039395445561</v>
       </c>
       <c r="EH13" s="1">
-        <f t="shared" si="24"/>
-        <v>12187.348315627152</v>
+        <f t="shared" si="31"/>
+        <v>13015.569001491105</v>
       </c>
       <c r="EI13" s="1">
-        <f t="shared" si="24"/>
-        <v>12065.47483247088</v>
+        <f t="shared" si="31"/>
+        <v>12885.413311476193</v>
       </c>
       <c r="EJ13" s="1">
-        <f t="shared" si="24"/>
-        <v>11944.820084146171</v>
+        <f t="shared" si="31"/>
+        <v>12756.559178361431</v>
       </c>
       <c r="EK13" s="1">
-        <f t="shared" si="24"/>
-        <v>11825.37188330471</v>
+        <f t="shared" si="31"/>
+        <v>12628.993586577817</v>
       </c>
       <c r="EL13" s="1">
-        <f t="shared" si="24"/>
-        <v>11707.118164471662</v>
+        <f t="shared" si="31"/>
+        <v>12502.703650712039</v>
       </c>
       <c r="EM13" s="1">
-        <f t="shared" si="24"/>
-        <v>11590.046982826945</v>
+        <f t="shared" si="31"/>
+        <v>12377.676614204918</v>
       </c>
       <c r="EN13" s="1">
-        <f t="shared" si="24"/>
-        <v>11474.146512998675</v>
+        <f t="shared" si="31"/>
+        <v>12253.899848062869</v>
       </c>
       <c r="EO13" s="1">
-        <f t="shared" si="24"/>
-        <v>11359.40504786869</v>
+        <f t="shared" si="31"/>
+        <v>12131.360849582241</v>
       </c>
       <c r="EP13" s="1">
-        <f t="shared" si="24"/>
-        <v>11245.810997390003</v>
+        <f t="shared" si="31"/>
+        <v>12010.047241086419</v>
       </c>
       <c r="EQ13" s="1">
-        <f t="shared" si="24"/>
-        <v>11133.352887416102</v>
+        <f t="shared" si="31"/>
+        <v>11889.946768675554</v>
       </c>
       <c r="ER13" s="1">
-        <f t="shared" si="24"/>
-        <v>11022.01935854194</v>
+        <f t="shared" si="31"/>
+        <v>11771.047300988799</v>
       </c>
       <c r="ES13" s="1">
-        <f t="shared" si="24"/>
-        <v>10911.799164956521</v>
+        <f t="shared" si="31"/>
+        <v>11653.336827978912</v>
       </c>
       <c r="ET13" s="1">
-        <f t="shared" si="24"/>
-        <v>10802.681173306955</v>
+        <f t="shared" si="31"/>
+        <v>11536.803459699122</v>
       </c>
       <c r="EU13" s="1">
-        <f t="shared" si="24"/>
-        <v>10694.654361573886</v>
+        <f t="shared" si="31"/>
+        <v>11421.43542510213</v>
       </c>
       <c r="EV13" s="1">
-        <f t="shared" si="24"/>
-        <v>10587.707817958148</v>
+        <f t="shared" si="31"/>
+        <v>11307.221070851108</v>
       </c>
       <c r="EW13" s="1">
-        <f t="shared" si="24"/>
-        <v>10481.830739778567</v>
+        <f t="shared" si="31"/>
+        <v>11194.148860142597</v>
       </c>
       <c r="EX13" s="1">
-        <f t="shared" si="24"/>
-        <v>10377.012432380781</v>
+        <f t="shared" si="31"/>
+        <v>11082.207371541172</v>
       </c>
       <c r="EY13" s="1">
-        <f t="shared" si="24"/>
-        <v>10273.242308056973</v>
+        <f t="shared" si="31"/>
+        <v>10971.38529782576</v>
       </c>
       <c r="EZ13" s="1">
-        <f t="shared" si="24"/>
-        <v>10170.509884976404</v>
+        <f t="shared" si="31"/>
+        <v>10861.671444847503</v>
       </c>
     </row>
     <row r="14" spans="1:156" x14ac:dyDescent="0.3">
@@ -2809,10 +2926,22 @@
         <f>8016.8</f>
         <v>8016.8</v>
       </c>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
+      <c r="O14" s="2">
+        <f>8016.8</f>
+        <v>8016.8</v>
+      </c>
+      <c r="P14" s="2">
+        <f>8016.8</f>
+        <v>8016.8</v>
+      </c>
+      <c r="Q14" s="2">
+        <f t="shared" ref="Q14:R14" si="32">8016.8</f>
+        <v>8016.8</v>
+      </c>
+      <c r="R14" s="2">
+        <f t="shared" si="32"/>
+        <v>8016.8</v>
+      </c>
       <c r="T14" s="2">
         <v>8053</v>
       </c>
@@ -2829,51 +2958,51 @@
         <v>8053</v>
       </c>
       <c r="Y14" s="2">
-        <f t="shared" ref="Y14:AJ14" si="25">8016.8</f>
+        <f t="shared" ref="Y14:AJ14" si="33">8016.8</f>
         <v>8016.8</v>
       </c>
       <c r="Z14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AA14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AB14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AC14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AD14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AE14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AF14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AG14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AH14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AI14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
       <c r="AJ14" s="2">
-        <f t="shared" si="25"/>
+        <f t="shared" si="33"/>
         <v>8016.8</v>
       </c>
     </row>
@@ -2882,124 +3011,136 @@
         <v>22</v>
       </c>
       <c r="C15" s="8">
-        <f t="shared" ref="C15:K15" si="26">C13/C14</f>
+        <f t="shared" ref="C15:K15" si="34">C13/C14</f>
         <v>0.25414501361049247</v>
       </c>
       <c r="D15" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.63709477852016827</v>
       </c>
       <c r="E15" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>-0.22246968572135609</v>
       </c>
       <c r="F15" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.7764167285325414</v>
       </c>
       <c r="G15" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.20700321702548874</v>
       </c>
       <c r="H15" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.97636723583271467</v>
       </c>
       <c r="I15" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>5.6050482553823312E-2</v>
       </c>
       <c r="J15" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.67978223212076216</v>
       </c>
       <c r="K15" s="8">
-        <f t="shared" si="26"/>
+        <f t="shared" si="34"/>
         <v>0.63380106792499691</v>
       </c>
       <c r="L15" s="8">
-        <f t="shared" ref="L15:N15" si="27">L13/L14</f>
+        <f t="shared" ref="L15:O15" si="35">L13/L14</f>
         <v>0.5599442668225868</v>
       </c>
       <c r="M15" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v>0.56974630915926017</v>
       </c>
       <c r="N15" s="8">
-        <f t="shared" si="27"/>
+        <f t="shared" si="35"/>
         <v>0.65537371519808396</v>
       </c>
-      <c r="O15" s="8"/>
-      <c r="P15" s="8"/>
-      <c r="Q15" s="8"/>
-      <c r="R15" s="8"/>
+      <c r="O15" s="8">
+        <f t="shared" si="35"/>
+        <v>0.55969963077537166</v>
+      </c>
+      <c r="P15" s="8">
+        <f t="shared" ref="O15:P15" si="36">P13/P14</f>
+        <v>0.87640953996607118</v>
+      </c>
+      <c r="Q15" s="8">
+        <f t="shared" ref="Q15:R15" si="37">Q13/Q14</f>
+        <v>0.61508174333898835</v>
+      </c>
+      <c r="R15" s="8">
+        <f t="shared" si="37"/>
+        <v>0.63231135565312868</v>
+      </c>
       <c r="T15" s="8">
-        <f t="shared" ref="T15:Z15" si="28">T13/T14</f>
+        <f t="shared" ref="T15:Z15" si="38">T13/T14</f>
         <v>1.8478827766049919</v>
       </c>
       <c r="U15" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>1.6776356637278034</v>
       </c>
       <c r="V15" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>1.6978765677387309</v>
       </c>
       <c r="W15" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>1.4503911585744442</v>
       </c>
       <c r="X15" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>1.9261144914938533</v>
       </c>
       <c r="Y15" s="8">
-        <f t="shared" si="28"/>
+        <f t="shared" si="38"/>
         <v>2.4244087416425506</v>
       </c>
       <c r="Z15" s="8">
-        <f t="shared" si="28"/>
-        <v>2.9373500773375918</v>
+        <f t="shared" si="38"/>
+        <v>2.6605192840035925</v>
       </c>
       <c r="AA15" s="8">
-        <f t="shared" ref="AA15:AJ15" si="29">AA13/AA14</f>
-        <v>3.7136596750573809</v>
+        <f t="shared" ref="AA15:AJ15" si="39">AA13/AA14</f>
+        <v>3.2959205551965867</v>
       </c>
       <c r="AB15" s="8">
-        <f t="shared" si="29"/>
-        <v>3.7908331067146492</v>
+        <f t="shared" si="39"/>
+        <v>4.0569767361201485</v>
       </c>
       <c r="AC15" s="8">
-        <f t="shared" si="29"/>
-        <v>3.8695790093866274</v>
+        <f t="shared" si="39"/>
+        <v>4.1383163004304153</v>
       </c>
       <c r="AD15" s="8">
-        <f t="shared" si="29"/>
-        <v>3.9499291225174185</v>
+        <f t="shared" si="39"/>
+        <v>4.2212846563227693</v>
       </c>
       <c r="AE15" s="8">
-        <f t="shared" si="29"/>
-        <v>4.031915823240257</v>
+        <f t="shared" si="39"/>
+        <v>4.3059143996318046</v>
       </c>
       <c r="AF15" s="8">
-        <f t="shared" si="29"/>
-        <v>4.0722349814726631</v>
+        <f t="shared" si="39"/>
+        <v>4.3489735436281229</v>
       </c>
       <c r="AG15" s="8">
-        <f t="shared" si="29"/>
-        <v>4.1129573312873875</v>
+        <f t="shared" si="39"/>
+        <v>4.3924632790644038</v>
       </c>
       <c r="AH15" s="8">
-        <f t="shared" si="29"/>
-        <v>4.1540869046002618</v>
+        <f t="shared" si="39"/>
+        <v>4.4363879118550473</v>
       </c>
       <c r="AI15" s="8">
-        <f t="shared" si="29"/>
-        <v>4.1956277736462644</v>
+        <f t="shared" si="39"/>
+        <v>4.4807517909735983</v>
       </c>
       <c r="AJ15" s="8">
-        <f t="shared" si="29"/>
-        <v>4.2375840513827256</v>
+        <f t="shared" si="39"/>
+        <v>4.5255593088833361</v>
       </c>
     </row>
     <row r="17" spans="2:39" x14ac:dyDescent="0.3">
@@ -3015,100 +3156,112 @@
         <v>7.5807556739116544E-2</v>
       </c>
       <c r="H17" s="10">
-        <f t="shared" ref="H17:N17" si="30">H3/D3-1</f>
+        <f t="shared" ref="H17:P17" si="40">H3/D3-1</f>
         <v>5.7392760648702357E-2</v>
       </c>
       <c r="I17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>5.2292671435021809E-2</v>
       </c>
       <c r="J17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>5.6934555739783566E-2</v>
       </c>
       <c r="K17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>6.045265625307783E-2</v>
       </c>
       <c r="L17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>4.765764205107903E-2</v>
       </c>
       <c r="M17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>5.4625506828188453E-2</v>
       </c>
       <c r="N17" s="10">
-        <f t="shared" si="30"/>
+        <f t="shared" si="40"/>
         <v>4.1329273075414674E-2</v>
       </c>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
+      <c r="O17" s="10">
+        <f t="shared" si="40"/>
+        <v>2.5391931049855154E-2</v>
+      </c>
+      <c r="P17" s="10">
+        <f t="shared" si="40"/>
+        <v>4.7639294888829786E-2</v>
+      </c>
+      <c r="Q17" s="10">
+        <f t="shared" ref="Q17" si="41">Q3/M3-1</f>
+        <v>5.0000000000000044E-2</v>
+      </c>
+      <c r="R17" s="10">
+        <f t="shared" ref="R17" si="42">R3/N3-1</f>
+        <v>3.0000000000000027E-2</v>
+      </c>
       <c r="T17" s="10"/>
       <c r="U17" s="10">
-        <f t="shared" ref="U17:AJ17" si="31">U3/T3-1</f>
+        <f t="shared" ref="U17:AJ17" si="43">U3/T3-1</f>
         <v>6.7155377086975498E-2</v>
       </c>
       <c r="V17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.4327954345069625E-2</v>
       </c>
       <c r="W17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>6.7280193590965709E-2</v>
       </c>
       <c r="X17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>6.02595499019285E-2</v>
       </c>
       <c r="Y17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>5.0700096432015451E-2</v>
       </c>
       <c r="Z17" s="10">
-        <f t="shared" si="31"/>
-        <v>4.0000000000000036E-2</v>
+        <f t="shared" si="43"/>
+        <v>3.8274000161530708E-2</v>
       </c>
       <c r="AA17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>3.0000000000000027E-2</v>
       </c>
       <c r="AB17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AC17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AD17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AE17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>2.0000000000000018E-2</v>
       </c>
       <c r="AF17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AG17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AH17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AI17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
       <c r="AJ17" s="10">
-        <f t="shared" si="31"/>
+        <f t="shared" si="43"/>
         <v>1.0000000000000009E-2</v>
       </c>
     </row>
@@ -3125,115 +3278,127 @@
         <v>0.24219051544233575</v>
       </c>
       <c r="E18" s="10">
-        <f t="shared" ref="E18:N18" si="32">E5/E3</f>
+        <f t="shared" ref="E18:O18" si="44">E5/E3</f>
         <v>0.24343478630744766</v>
       </c>
       <c r="F18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.23544938066907248</v>
       </c>
       <c r="G18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.24305158863040952</v>
       </c>
       <c r="H18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.24612700455355374</v>
       </c>
       <c r="I18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.24639312454914056</v>
       </c>
       <c r="J18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.23971093731976839</v>
       </c>
       <c r="K18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.24814250687272457</v>
       </c>
       <c r="L18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.25112941801753919</v>
       </c>
       <c r="M18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.24912140009906361</v>
       </c>
       <c r="N18" s="10">
-        <f t="shared" si="32"/>
+        <f t="shared" si="44"/>
         <v>0.24581011774870676</v>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
+      <c r="O18" s="10">
+        <f t="shared" si="44"/>
+        <v>0.24941881177955305</v>
+      </c>
+      <c r="P18" s="10">
+        <f t="shared" ref="O18:P18" si="45">P5/P3</f>
+        <v>0.25158115466567454</v>
+      </c>
+      <c r="Q18" s="10">
+        <f t="shared" ref="Q18:R18" si="46">Q5/Q3</f>
+        <v>0.25</v>
+      </c>
+      <c r="R18" s="10">
+        <f t="shared" si="46"/>
+        <v>0.25</v>
+      </c>
       <c r="T18" s="10">
-        <f t="shared" ref="T18:AJ18" si="33">T5/T3</f>
+        <f t="shared" ref="T18:AJ18" si="47">T5/T3</f>
         <v>0.24688528219495995</v>
       </c>
       <c r="U18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.24829786587165184</v>
       </c>
       <c r="V18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.25098733487675334</v>
       </c>
       <c r="W18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.24140463839525986</v>
       </c>
       <c r="X18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.24375390549662487</v>
       </c>
       <c r="Y18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.24851061330278934</v>
       </c>
       <c r="Z18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.25</v>
       </c>
       <c r="AA18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
+        <v>0.25</v>
+      </c>
+      <c r="AB18" s="10">
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
-      <c r="AB18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AC18" s="10">
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
-      <c r="AC18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AD18" s="10">
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
-      <c r="AD18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AE18" s="10">
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
-      <c r="AE18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AF18" s="10">
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
-      <c r="AF18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AG18" s="10">
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
-      <c r="AG18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AH18" s="10">
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
-      <c r="AH18" s="10">
-        <f t="shared" si="33"/>
+      <c r="AI18" s="10">
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
-      <c r="AI18" s="10">
-        <f t="shared" si="33"/>
-        <v>0.26</v>
-      </c>
       <c r="AJ18" s="10">
-        <f t="shared" si="33"/>
+        <f t="shared" si="47"/>
         <v>0.26</v>
       </c>
       <c r="AL18" t="s">
@@ -3256,115 +3421,127 @@
         <v>0.19735180787523143</v>
       </c>
       <c r="E19" s="10">
-        <f t="shared" ref="E19:N19" si="34">E6/E3</f>
+        <f t="shared" ref="E19:O19" si="48">E6/E3</f>
         <v>0.22579885219189466</v>
       </c>
       <c r="F19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.20155076562957183</v>
       </c>
       <c r="G19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.20208009139795535</v>
       </c>
       <c r="H19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.20086369035834489</v>
       </c>
       <c r="I19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.20782443222805402</v>
       </c>
       <c r="J19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.19787413200452164</v>
       </c>
       <c r="K19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.20578547192708721</v>
       </c>
       <c r="L19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.20424011574689224</v>
       </c>
       <c r="M19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.20956671462603485</v>
       </c>
       <c r="N19" s="10">
-        <f t="shared" si="34"/>
+        <f t="shared" si="48"/>
         <v>0.20228297351484875</v>
       </c>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
+      <c r="O19" s="10">
+        <f t="shared" si="48"/>
+        <v>0.20633540447680984</v>
+      </c>
+      <c r="P19" s="10">
+        <f t="shared" ref="O19:P19" si="49">P6/P3</f>
+        <v>0.21051059176333975</v>
+      </c>
+      <c r="Q19" s="10">
+        <f t="shared" ref="Q19:R19" si="50">Q6/Q3</f>
+        <v>0.21</v>
+      </c>
+      <c r="R19" s="10">
+        <f t="shared" si="50"/>
+        <v>0.21</v>
+      </c>
       <c r="T19" s="10">
-        <f t="shared" ref="T19:AJ19" si="35">T6/T3</f>
+        <f t="shared" ref="T19:AJ19" si="51">T6/T3</f>
         <v>0.20763067691673473</v>
       </c>
       <c r="U19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.20797244393732642</v>
       </c>
       <c r="V19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.20569389301515137</v>
       </c>
       <c r="W19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.20798672968105103</v>
       </c>
       <c r="X19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.20207675988428159</v>
       </c>
       <c r="Y19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.20541421617216238</v>
       </c>
       <c r="Z19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
+        <v>0.20926976774538206</v>
+      </c>
+      <c r="AA19" s="10">
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
-      <c r="AA19" s="10">
-        <f t="shared" si="35"/>
-        <v>0.19999999999999998</v>
-      </c>
       <c r="AB19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AC19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AD19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AE19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AF19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AG19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AH19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AI19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AJ19" s="10">
-        <f t="shared" si="35"/>
+        <f t="shared" si="51"/>
         <v>0.2</v>
       </c>
       <c r="AL19" t="s">
@@ -3387,123 +3564,135 @@
         <v>4.4838707567104327E-2</v>
       </c>
       <c r="E20" s="10">
-        <f t="shared" ref="E20:N20" si="36">E7/E3</f>
+        <f t="shared" ref="E20:O20" si="52">E7/E3</f>
         <v>1.7635934115552997E-2</v>
       </c>
       <c r="F20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>3.3898615039500632E-2</v>
       </c>
       <c r="G20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>4.0971497232454156E-2</v>
       </c>
       <c r="H20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>4.5263314195208869E-2</v>
       </c>
       <c r="I20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>3.8568692321086541E-2</v>
       </c>
       <c r="J20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>4.1836805315246729E-2</v>
       </c>
       <c r="K20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>4.2357034945637369E-2</v>
       </c>
       <c r="L20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>4.6889302270646943E-2</v>
       </c>
       <c r="M20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>3.9554685473028754E-2</v>
       </c>
       <c r="N20" s="10">
-        <f t="shared" si="36"/>
+        <f t="shared" si="52"/>
         <v>4.3527144233858013E-2</v>
       </c>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
+      <c r="O20" s="10">
+        <f t="shared" si="52"/>
+        <v>4.308340730274321E-2</v>
+      </c>
+      <c r="P20" s="10">
+        <f t="shared" ref="O20:P20" si="53">P7/P3</f>
+        <v>4.1070562902334809E-2</v>
+      </c>
+      <c r="Q20" s="10">
+        <f t="shared" ref="Q20:R20" si="54">Q7/Q3</f>
+        <v>4.0000000000000022E-2</v>
+      </c>
+      <c r="R20" s="10">
+        <f t="shared" si="54"/>
+        <v>4.0000000000000015E-2</v>
+      </c>
       <c r="T20" s="10">
-        <f t="shared" ref="T20:AJ20" si="37">T7/T3</f>
+        <f t="shared" ref="T20:AJ20" si="55">T7/T3</f>
         <v>3.9254605278225219E-2</v>
       </c>
       <c r="U20" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>4.032542193432543E-2</v>
       </c>
       <c r="V20" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>4.5293441861602016E-2</v>
       </c>
       <c r="W20" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>3.3417908714208827E-2</v>
       </c>
       <c r="X20" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>4.16771456123433E-2</v>
       </c>
       <c r="Y20" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
         <v>4.3096397130626962E-2</v>
       </c>
       <c r="Z20" s="10">
-        <f t="shared" si="37"/>
-        <v>0.05</v>
+        <f t="shared" si="55"/>
+        <v>4.0730232254617929E-2</v>
       </c>
       <c r="AA20" s="10">
-        <f t="shared" si="37"/>
+        <f t="shared" si="55"/>
+        <v>4.9999999999999989E-2</v>
+      </c>
+      <c r="AB20" s="10">
+        <f t="shared" si="55"/>
+        <v>5.9999999999999991E-2</v>
+      </c>
+      <c r="AC20" s="10">
+        <f t="shared" si="55"/>
+        <v>5.9999999999999984E-2</v>
+      </c>
+      <c r="AD20" s="10">
+        <f t="shared" si="55"/>
+        <v>0.06</v>
+      </c>
+      <c r="AE20" s="10">
+        <f t="shared" si="55"/>
+        <v>5.9999999999999991E-2</v>
+      </c>
+      <c r="AF20" s="10">
+        <f t="shared" si="55"/>
+        <v>5.9999999999999984E-2</v>
+      </c>
+      <c r="AG20" s="10">
+        <f t="shared" si="55"/>
+        <v>5.9999999999999991E-2</v>
+      </c>
+      <c r="AH20" s="10">
+        <f t="shared" si="55"/>
+        <v>5.9999999999999977E-2</v>
+      </c>
+      <c r="AI20" s="10">
+        <f t="shared" si="55"/>
+        <v>5.9999999999999984E-2</v>
+      </c>
+      <c r="AJ20" s="10">
+        <f t="shared" si="55"/>
         <v>6.0000000000000012E-2</v>
-      </c>
-      <c r="AB20" s="10">
-        <f t="shared" si="37"/>
-        <v>5.9999999999999991E-2</v>
-      </c>
-      <c r="AC20" s="10">
-        <f t="shared" si="37"/>
-        <v>6.0000000000000019E-2</v>
-      </c>
-      <c r="AD20" s="10">
-        <f t="shared" si="37"/>
-        <v>0.06</v>
-      </c>
-      <c r="AE20" s="10">
-        <f t="shared" si="37"/>
-        <v>5.9999999999999984E-2</v>
-      </c>
-      <c r="AF20" s="10">
-        <f t="shared" si="37"/>
-        <v>6.0000000000000019E-2</v>
-      </c>
-      <c r="AG20" s="10">
-        <f t="shared" si="37"/>
-        <v>0.06</v>
-      </c>
-      <c r="AH20" s="10">
-        <f t="shared" si="37"/>
-        <v>0.06</v>
-      </c>
-      <c r="AI20" s="10">
-        <f t="shared" si="37"/>
-        <v>6.0000000000000012E-2</v>
-      </c>
-      <c r="AJ20" s="10">
-        <f t="shared" si="37"/>
-        <v>5.9999999999999991E-2</v>
       </c>
       <c r="AL20" t="s">
         <v>42</v>
       </c>
       <c r="AM20" s="2">
         <f>NPV(AM19,Y13:EZ13)</f>
-        <v>575734.52836828528</v>
+        <v>605606.93586661096</v>
       </c>
     </row>
     <row r="21" spans="2:39" x14ac:dyDescent="0.3">
@@ -3519,115 +3708,127 @@
         <v>0.225316074653823</v>
       </c>
       <c r="E21" s="10">
-        <f t="shared" ref="E21:N21" si="38">E11/E10</f>
+        <f t="shared" ref="E21:O21" si="56">E11/E10</f>
         <v>-0.23480083857442349</v>
       </c>
       <c r="F21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.34745001123343067</v>
       </c>
       <c r="G21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.29464285714285715</v>
       </c>
       <c r="H21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.24927752400484757</v>
       </c>
       <c r="I21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.29726775956284152</v>
       </c>
       <c r="J21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.24474594306996542</v>
       </c>
       <c r="K21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.24562899786780384</v>
       </c>
       <c r="L21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.24175116690809592</v>
       </c>
       <c r="M21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.22695965890455888</v>
       </c>
       <c r="N21" s="10">
-        <f t="shared" si="38"/>
+        <f t="shared" si="56"/>
         <v>0.22088180382019246</v>
       </c>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
+      <c r="O21" s="10">
+        <f t="shared" si="56"/>
+        <v>0.2260593927260594</v>
+      </c>
+      <c r="P21" s="10">
+        <f t="shared" ref="O21:P21" si="57">P11/P10</f>
+        <v>0.23264298744500483</v>
+      </c>
+      <c r="Q21" s="10">
+        <f t="shared" ref="Q21:R21" si="58">Q11/Q10</f>
+        <v>0.23</v>
+      </c>
+      <c r="R21" s="10">
+        <f t="shared" si="58"/>
+        <v>0.23</v>
+      </c>
       <c r="T21" s="10">
-        <f t="shared" ref="T21:AJ21" si="39">T11/T10</f>
+        <f t="shared" ref="T21:AJ21" si="59">T11/T10</f>
         <v>0.24433286935772519</v>
       </c>
       <c r="U21" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="59"/>
         <v>0.33349542890488232</v>
       </c>
       <c r="V21" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="59"/>
         <v>0.25438596491228072</v>
       </c>
       <c r="W21" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="59"/>
         <v>0.33638928067700985</v>
       </c>
       <c r="X21" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="59"/>
         <v>0.25530941047235445</v>
       </c>
       <c r="Y21" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="59"/>
         <v>0.23383632977308144</v>
       </c>
       <c r="Z21" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="59"/>
+        <v>0.23151764663364485</v>
+      </c>
+      <c r="AA21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AA21" s="10">
-        <f t="shared" si="39"/>
+      <c r="AB21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AB21" s="10">
-        <f t="shared" si="39"/>
+      <c r="AC21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AC21" s="10">
-        <f t="shared" si="39"/>
+      <c r="AD21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AD21" s="10">
-        <f t="shared" si="39"/>
+      <c r="AE21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AE21" s="10">
-        <f t="shared" si="39"/>
+      <c r="AF21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AF21" s="10">
-        <f t="shared" si="39"/>
+      <c r="AG21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AG21" s="10">
-        <f t="shared" si="39"/>
+      <c r="AH21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AH21" s="10">
-        <f t="shared" si="39"/>
+      <c r="AI21" s="10">
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
-      <c r="AI21" s="10">
-        <f t="shared" si="39"/>
-        <v>0.25</v>
-      </c>
       <c r="AJ21" s="10">
-        <f t="shared" si="39"/>
+        <f t="shared" si="59"/>
         <v>0.25</v>
       </c>
       <c r="AL21" t="s">
@@ -3635,7 +3836,7 @@
       </c>
       <c r="AM21" s="2">
         <f>Main!D8</f>
-        <v>-30030</v>
+        <v>-34057</v>
       </c>
     </row>
     <row r="22" spans="2:39" x14ac:dyDescent="0.3">
@@ -3651,123 +3852,135 @@
         <v>3.3684637476367109E-2</v>
       </c>
       <c r="E22" s="10">
-        <f t="shared" ref="E22:N22" si="40">E13/E3</f>
+        <f t="shared" ref="E22:O22" si="60">E13/E3</f>
         <v>-1.1766014671526636E-2</v>
       </c>
       <c r="F22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>3.8250999707402714E-2</v>
       </c>
       <c r="G22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>1.0984826100944839E-2</v>
       </c>
       <c r="H22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>4.8820778063749751E-2</v>
       </c>
       <c r="I22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>2.8170941021367626E-3</v>
       </c>
       <c r="J22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>3.168616051860567E-2</v>
       </c>
       <c r="K22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>3.1602149738712636E-2</v>
       </c>
       <c r="L22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>2.6580447042844065E-2</v>
       </c>
       <c r="M22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>2.6988937896549284E-2</v>
       </c>
       <c r="N22" s="10">
-        <f t="shared" si="40"/>
+        <f t="shared" si="60"/>
         <v>2.9099327624976461E-2</v>
       </c>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
+      <c r="O22" s="10">
+        <f t="shared" si="60"/>
+        <v>2.7093938131381747E-2</v>
+      </c>
+      <c r="P22" s="10">
+        <f t="shared" ref="O22:P22" si="61">P13/P3</f>
+        <v>3.9604964994757672E-2</v>
+      </c>
+      <c r="Q22" s="10">
+        <f t="shared" ref="Q22:R22" si="62">Q13/Q3</f>
+        <v>2.7691690449795987E-2</v>
+      </c>
+      <c r="R22" s="10">
+        <f t="shared" si="62"/>
+        <v>2.7257604862531523E-2</v>
+      </c>
       <c r="T22" s="10">
-        <f t="shared" ref="T22:AJ22" si="41">T13/T3</f>
+        <f t="shared" ref="T22:AJ22" si="63">T13/T3</f>
         <v>2.8400806162255422E-2</v>
       </c>
       <c r="U22" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>2.4161630758059986E-2</v>
       </c>
       <c r="V22" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>2.3872378019184501E-2</v>
       </c>
       <c r="W22" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>1.9107165350595218E-2</v>
       </c>
       <c r="X22" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>2.3932111861137896E-2</v>
       </c>
       <c r="Y22" s="10">
-        <f t="shared" si="41"/>
+        <f t="shared" si="63"/>
         <v>2.8541010448100913E-2</v>
       </c>
       <c r="Z22" s="10">
-        <f t="shared" si="41"/>
-        <v>3.3249557767283937E-2</v>
+        <f t="shared" si="63"/>
+        <v>3.0166014509149592E-2</v>
       </c>
       <c r="AA22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.0812673150443478E-2</v>
+        <f t="shared" si="63"/>
+        <v>3.6281984602969199E-2</v>
       </c>
       <c r="AB22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.0843921452890092E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.3784122008822451E-2</v>
       </c>
       <c r="AC22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.0874863399430403E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.378623845971634E-2</v>
       </c>
       <c r="AD22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.0905501993553618E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.378833416109168E-2</v>
       </c>
       <c r="AE22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.0935840209303083E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.3790409316375081E-2</v>
       </c>
       <c r="AF22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.0935840209303118E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.3790409316375081E-2</v>
       </c>
       <c r="AG22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.093584020930309E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.3790409316375081E-2</v>
       </c>
       <c r="AH22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.0935840209303097E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.3790409316375074E-2</v>
       </c>
       <c r="AI22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.0935840209303104E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.3790409316375081E-2</v>
       </c>
       <c r="AJ22" s="10">
-        <f t="shared" si="41"/>
-        <v>4.093584020930309E-2</v>
+        <f t="shared" si="63"/>
+        <v>4.3790409316375102E-2</v>
       </c>
       <c r="AL22" t="s">
         <v>44</v>
       </c>
       <c r="AM22" s="2">
         <f>AM20+AM21</f>
-        <v>545704.52836828528</v>
+        <v>571549.93586661096</v>
       </c>
     </row>
     <row r="23" spans="2:39" x14ac:dyDescent="0.3">
@@ -3776,7 +3989,7 @@
       </c>
       <c r="AM23" s="6">
         <f>AM22/AJ14</f>
-        <v>68.07011879656288</v>
+        <v>71.294024531809569</v>
       </c>
     </row>
     <row r="24" spans="2:39" x14ac:dyDescent="0.3">
@@ -3785,7 +3998,7 @@
       </c>
       <c r="AM24" s="6">
         <f>Main!D3</f>
-        <v>95.91</v>
+        <v>99.35</v>
       </c>
     </row>
     <row r="25" spans="2:39" x14ac:dyDescent="0.3">
@@ -3794,7 +4007,7 @@
       </c>
       <c r="AM25" s="11">
         <f>AM23/AM24-1</f>
-        <v>-0.29027089149658136</v>
+        <v>-0.28239532428978786</v>
       </c>
     </row>
     <row r="26" spans="2:39" x14ac:dyDescent="0.3">

--- a/Financial Analysis/WMT.xlsx
+++ b/Financial Analysis/WMT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\antos\Documents\GitHub\FinanceModels\Financial Analysis\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4E22C38-6EF7-4E64-921F-8987788E33B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94147595-A44E-4CBA-958C-4DC0163BC375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{4FE1C73D-B38E-414F-97D3-844DCE1F8905}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{4FE1C73D-B38E-414F-97D3-844DCE1F8905}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -248,7 +248,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -267,7 +267,6 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -720,7 +719,7 @@
       </c>
       <c r="F3" s="4">
         <f ca="1">TODAY()</f>
-        <v>45904</v>
+        <v>45965</v>
       </c>
       <c r="G3" s="4">
         <v>45981</v>
@@ -1209,7 +1208,7 @@
         <f>SUM(K4:N4)</f>
         <v>511753</v>
       </c>
-      <c r="Z4" s="12">
+      <c r="Z4" s="2">
         <f>SUM(O4:R4)</f>
         <v>530102.51500000001</v>
       </c>
@@ -1312,7 +1311,7 @@
         <v>41306</v>
       </c>
       <c r="P5" s="7">
-        <f t="shared" ref="O5:P5" si="4">P3-P4</f>
+        <f t="shared" ref="P5" si="4">P3-P4</f>
         <v>44631</v>
       </c>
       <c r="Q5" s="7">
@@ -1467,7 +1466,7 @@
         <f>SUM(K6:N6)</f>
         <v>139884</v>
       </c>
-      <c r="Z6" s="12">
+      <c r="Z6" s="2">
         <f>SUM(O6:R6)</f>
         <v>147963.98420000001</v>
       </c>
@@ -1570,7 +1569,7 @@
         <v>7135</v>
       </c>
       <c r="P7" s="7">
-        <f t="shared" ref="O7:R7" si="10">P5-P6</f>
+        <f t="shared" ref="P7:R7" si="10">P5-P6</f>
         <v>7286</v>
       </c>
       <c r="Q7" s="7">
@@ -1725,7 +1724,7 @@
         <f>SUM(K8:N8)</f>
         <v>2245</v>
       </c>
-      <c r="Z8" s="12">
+      <c r="Z8" s="2">
         <f t="shared" ref="Z8:Z9" si="13">SUM(O8:R8)</f>
         <v>2320.6</v>
       </c>
@@ -1844,7 +1843,7 @@
         <f>SUM(K9:N9)</f>
         <v>794</v>
       </c>
-      <c r="Z9" s="12">
+      <c r="Z9" s="2">
         <f t="shared" si="13"/>
         <v>-2111</v>
       </c>
@@ -1947,7 +1946,7 @@
         <v>5994</v>
       </c>
       <c r="P10" s="7">
-        <f t="shared" ref="O10:R10" si="18">P7-P8-P9</f>
+        <f t="shared" ref="P10:R10" si="18">P7-P8-P9</f>
         <v>9319</v>
       </c>
       <c r="Q10" s="7">
@@ -2102,7 +2101,7 @@
         <f>SUM(K11:N11)</f>
         <v>6152</v>
       </c>
-      <c r="Z11" s="12">
+      <c r="Z11" s="2">
         <f t="shared" ref="Z11:Z12" si="21">SUM(O11:R11)</f>
         <v>6618.7817840000007</v>
       </c>
@@ -2222,7 +2221,7 @@
         <f>SUM(K12:N12)</f>
         <v>721</v>
       </c>
-      <c r="Z12" s="12">
+      <c r="Z12" s="2">
         <f t="shared" si="21"/>
         <v>641.03801999999996</v>
       </c>
@@ -2325,7 +2324,7 @@
         <v>4487</v>
       </c>
       <c r="P13" s="7">
-        <f t="shared" ref="O13:P13" si="26">P10-P11-P12</f>
+        <f t="shared" ref="P13" si="26">P10-P11-P12</f>
         <v>7026</v>
       </c>
       <c r="Q13" s="7">
@@ -3063,7 +3062,7 @@
         <v>0.55969963077537166</v>
       </c>
       <c r="P15" s="8">
-        <f t="shared" ref="O15:P15" si="36">P13/P14</f>
+        <f t="shared" ref="P15" si="36">P13/P14</f>
         <v>0.87640953996607118</v>
       </c>
       <c r="Q15" s="8">
@@ -3322,7 +3321,7 @@
         <v>0.24941881177955305</v>
       </c>
       <c r="P18" s="10">
-        <f t="shared" ref="O18:P18" si="45">P5/P3</f>
+        <f t="shared" ref="P18" si="45">P5/P3</f>
         <v>0.25158115466567454</v>
       </c>
       <c r="Q18" s="10">
@@ -3465,7 +3464,7 @@
         <v>0.20633540447680984</v>
       </c>
       <c r="P19" s="10">
-        <f t="shared" ref="O19:P19" si="49">P6/P3</f>
+        <f t="shared" ref="P19" si="49">P6/P3</f>
         <v>0.21051059176333975</v>
       </c>
       <c r="Q19" s="10">
@@ -3608,7 +3607,7 @@
         <v>4.308340730274321E-2</v>
       </c>
       <c r="P20" s="10">
-        <f t="shared" ref="O20:P20" si="53">P7/P3</f>
+        <f t="shared" ref="P20" si="53">P7/P3</f>
         <v>4.1070562902334809E-2</v>
       </c>
       <c r="Q20" s="10">
@@ -3752,7 +3751,7 @@
         <v>0.2260593927260594</v>
       </c>
       <c r="P21" s="10">
-        <f t="shared" ref="O21:P21" si="57">P11/P10</f>
+        <f t="shared" ref="P21" si="57">P11/P10</f>
         <v>0.23264298744500483</v>
       </c>
       <c r="Q21" s="10">
@@ -3896,7 +3895,7 @@
         <v>2.7093938131381747E-2</v>
       </c>
       <c r="P22" s="10">
-        <f t="shared" ref="O22:P22" si="61">P13/P3</f>
+        <f t="shared" ref="P22" si="61">P13/P3</f>
         <v>3.9604964994757672E-2</v>
       </c>
       <c r="Q22" s="10">
